--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>177.573</v>
+        <v>1082.132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>172.29</v>
+        <v>1143.352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>162.283</v>
+        <v>1191.495</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>156.43</v>
+        <v>1257.255</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>144.313</v>
+        <v>1260.135</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>135.558</v>
+        <v>1299.366</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>131.185</v>
+        <v>1341.428</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>126.733</v>
+        <v>1372.732</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>131.235</v>
+        <v>1407.986</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>128.687</v>
+        <v>1429.29</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>126.361</v>
+        <v>1437.35</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>125.147</v>
+        <v>1456.504</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>129.272</v>
+        <v>1473.847</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>129.064</v>
+        <v>1461.335</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>118.502</v>
+        <v>1456.789</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>119.618</v>
+        <v>1455.575</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>112.846</v>
+        <v>1421.12</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>120.1</v>
+        <v>1411.242</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>118.942</v>
+        <v>1395.263</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>116.596</v>
+        <v>1386.174</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>117.78</v>
+        <v>1383.316</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>113.379</v>
+        <v>1380.241</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>108.661</v>
+        <v>1374.575</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>104.269</v>
+        <v>1379.222</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>94.523</v>
+        <v>1356.256</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>92.51600000000001</v>
+        <v>1354.258</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>91.985</v>
+        <v>1330.87</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>90.164</v>
+        <v>1318.589</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>96.399</v>
+        <v>1319.6</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>99.09999999999999</v>
+        <v>1308.95</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>91.349</v>
+        <v>1315.474</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>91.312</v>
+        <v>1301.813</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>104.049</v>
+        <v>1291.528</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>103.108</v>
+        <v>1293.452</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>102.311</v>
+        <v>1286.128</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>100.549</v>
+        <v>1283.178</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>100.752</v>
+        <v>1315.717</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B39">
-        <v>101.581</v>
+        <v>1310.433</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B40">
-        <v>102.282</v>
+        <v>1314.982</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B41">
-        <v>102.813</v>
+        <v>1320.026</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B42">
-        <v>101.048</v>
+        <v>1389.296</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B43">
-        <v>103.606</v>
+        <v>1388.653</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B44">
-        <v>106.81</v>
+        <v>1387.403</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B45">
-        <v>109.875</v>
+        <v>1384.574</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B46">
-        <v>113.642</v>
+        <v>1414.001</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B47">
-        <v>119.571</v>
+        <v>1399.882</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B48">
-        <v>125.654</v>
+        <v>1385.85</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B49">
-        <v>131.345</v>
+        <v>1371.337</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B50">
-        <v>139.944</v>
+        <v>1295.262</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B51">
-        <v>147.358</v>
+        <v>1275.362</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B52">
-        <v>155.268</v>
+        <v>1255.889</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B53">
-        <v>163.676</v>
+        <v>1234.858</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B54">
-        <v>173.134</v>
+        <v>1203.179</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B55">
-        <v>180.053</v>
+        <v>1188.576</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B56">
-        <v>187.611</v>
+        <v>1172.532</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B57">
-        <v>195.344</v>
+        <v>1157.572</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B58">
-        <v>209.702</v>
+        <v>1027.842</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B59">
-        <v>216.826</v>
+        <v>1009.383</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B60">
-        <v>225.029</v>
+        <v>990.6799999999999</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B61">
-        <v>233.312</v>
+        <v>973.548</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B62">
-        <v>221.3</v>
+        <v>935.727</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B63">
-        <v>226.323</v>
+        <v>913.913</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B64">
-        <v>232.152</v>
+        <v>893.477</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B65">
-        <v>238.068</v>
+        <v>870.798</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B66">
-        <v>245.109</v>
+        <v>844.655</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B67">
-        <v>247.26</v>
+        <v>828.869</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B68">
-        <v>248.325</v>
+        <v>812.37</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B69">
-        <v>248.465</v>
+        <v>797.398</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B70">
-        <v>229.332</v>
+        <v>814.52</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B71">
-        <v>229.944</v>
+        <v>793.128</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B72">
-        <v>232.055</v>
+        <v>773.705</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B73">
-        <v>233.663</v>
+        <v>753.728</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B74">
-        <v>217.665</v>
+        <v>697.6900000000001</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B75">
-        <v>222.889</v>
+        <v>698.513</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B76">
-        <v>230.394</v>
+        <v>700.638</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B77">
-        <v>241.271</v>
+        <v>702.925</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B78">
-        <v>265.716</v>
+        <v>709.741</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B79">
-        <v>281.786</v>
+        <v>721.796</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B80">
-        <v>299.201</v>
+        <v>732.838</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B81">
-        <v>317.365</v>
+        <v>745.074</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B82">
-        <v>351.929</v>
+        <v>773.1420000000001</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B83">
-        <v>363.251</v>
+        <v>794.522</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B84">
-        <v>375.35</v>
+        <v>817.8869999999999</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B85">
-        <v>388.224</v>
+        <v>838.121</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B86">
-        <v>401.236</v>
+        <v>918.673</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B87">
-        <v>411.585</v>
+        <v>950.28</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B88">
-        <v>422.299</v>
+        <v>981.497</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B89">
-        <v>431.896</v>
+        <v>1014.72</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B90">
-        <v>476.749</v>
+        <v>1053.564</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B91">
-        <v>484.721</v>
+        <v>1086.228</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B92">
-        <v>491.889</v>
+        <v>1121.841</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B93">
-        <v>500.485</v>
+        <v>1155.289</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>1082.132</v>
+        <v>618.601</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>1143.352</v>
+        <v>599.314</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>1191.495</v>
+        <v>580.867</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>1257.255</v>
+        <v>562.787</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>1260.135</v>
+        <v>512.5410000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>1299.366</v>
+        <v>497.734</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>1341.428</v>
+        <v>487.199</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>1372.732</v>
+        <v>469.97</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>1407.986</v>
+        <v>431.401</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>1429.29</v>
+        <v>409.884</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>1437.35</v>
+        <v>387.977</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>1456.504</v>
+        <v>373.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>1473.847</v>
+        <v>346.589</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>1461.335</v>
+        <v>332.338</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>1456.789</v>
+        <v>318.156</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>1455.575</v>
+        <v>303.706</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>1421.12</v>
+        <v>284.167</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>1411.242</v>
+        <v>271.479</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>1395.263</v>
+        <v>257.365</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>1386.174</v>
+        <v>246.023</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>1383.316</v>
+        <v>217.855</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>1380.241</v>
+        <v>206.371</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>1374.575</v>
+        <v>196.169</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>1379.222</v>
+        <v>185.19</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>1356.256</v>
+        <v>171.223</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>1354.258</v>
+        <v>169.573</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>1330.87</v>
+        <v>160.092</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>1318.589</v>
+        <v>158.022</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>1319.6</v>
+        <v>160.344</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>1308.95</v>
+        <v>154.678</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>1315.474</v>
+        <v>149.956</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>1301.813</v>
+        <v>146.924</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>1291.528</v>
+        <v>155.155</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>1293.452</v>
+        <v>149.545</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>1286.128</v>
+        <v>142.418</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46278.36458333334</v>
+        <v>46283.36458333334</v>
       </c>
       <c r="B37">
-        <v>1283.178</v>
+        <v>136.767</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46278.375</v>
+        <v>46283.375</v>
       </c>
       <c r="B38">
-        <v>1315.717</v>
+        <v>121.629</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46278.38541666666</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="B39">
-        <v>1310.433</v>
+        <v>126.044</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46278.39583333334</v>
+        <v>46283.39583333334</v>
       </c>
       <c r="B40">
-        <v>1314.982</v>
+        <v>130.753</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46278.40625</v>
+        <v>46283.40625</v>
       </c>
       <c r="B41">
-        <v>1320.026</v>
+        <v>135.795</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46278.41666666666</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B42">
-        <v>1389.296</v>
+        <v>147.548</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46278.42708333334</v>
+        <v>46283.42708333334</v>
       </c>
       <c r="B43">
-        <v>1388.653</v>
+        <v>153.511</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46278.4375</v>
+        <v>46283.4375</v>
       </c>
       <c r="B44">
-        <v>1387.403</v>
+        <v>160.134</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46278.44791666666</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="B45">
-        <v>1384.574</v>
+        <v>166.188</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46278.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B46">
-        <v>1414.001</v>
+        <v>184.307</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46278.46875</v>
+        <v>46283.46875</v>
       </c>
       <c r="B47">
-        <v>1399.882</v>
+        <v>188.589</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46278.47916666666</v>
+        <v>46283.47916666666</v>
       </c>
       <c r="B48">
-        <v>1385.85</v>
+        <v>193.36</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46278.48958333334</v>
+        <v>46283.48958333334</v>
       </c>
       <c r="B49">
-        <v>1371.337</v>
+        <v>196.816</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46278.5</v>
+        <v>46283.5</v>
       </c>
       <c r="B50">
-        <v>1295.262</v>
+        <v>206.122</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46278.51041666666</v>
+        <v>46283.51041666666</v>
       </c>
       <c r="B51">
-        <v>1275.362</v>
+        <v>209.198</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46278.52083333334</v>
+        <v>46283.52083333334</v>
       </c>
       <c r="B52">
-        <v>1255.889</v>
+        <v>211.707</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46278.53125</v>
+        <v>46283.53125</v>
       </c>
       <c r="B53">
-        <v>1234.858</v>
+        <v>214.337</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46278.54166666666</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B54">
-        <v>1203.179</v>
+        <v>212.487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46278.55208333334</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="B55">
-        <v>1188.576</v>
+        <v>216.797</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46278.5625</v>
+        <v>46283.5625</v>
       </c>
       <c r="B56">
-        <v>1172.532</v>
+        <v>221.003</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46278.57291666666</v>
+        <v>46283.57291666666</v>
       </c>
       <c r="B57">
-        <v>1157.572</v>
+        <v>226.776</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46278.58333333334</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B58">
-        <v>1027.842</v>
+        <v>232.609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46278.59375</v>
+        <v>46283.59375</v>
       </c>
       <c r="B59">
-        <v>1009.383</v>
+        <v>239.287</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46278.60416666666</v>
+        <v>46283.60416666666</v>
       </c>
       <c r="B60">
-        <v>990.6799999999999</v>
+        <v>246.266</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46278.61458333334</v>
+        <v>46283.61458333334</v>
       </c>
       <c r="B61">
-        <v>973.548</v>
+        <v>253.348</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46278.625</v>
+        <v>46283.625</v>
       </c>
       <c r="B62">
-        <v>935.727</v>
+        <v>262.609</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46278.63541666666</v>
+        <v>46283.63541666666</v>
       </c>
       <c r="B63">
-        <v>913.913</v>
+        <v>273.92</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46278.64583333334</v>
+        <v>46283.64583333334</v>
       </c>
       <c r="B64">
-        <v>893.477</v>
+        <v>284.545</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46278.65625</v>
+        <v>46283.65625</v>
       </c>
       <c r="B65">
-        <v>870.798</v>
+        <v>296.127</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46278.66666666666</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B66">
-        <v>844.655</v>
+        <v>270.833</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46278.67708333334</v>
+        <v>46283.67708333334</v>
       </c>
       <c r="B67">
-        <v>828.869</v>
+        <v>286.171</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46278.6875</v>
+        <v>46283.6875</v>
       </c>
       <c r="B68">
-        <v>812.37</v>
+        <v>301.043</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46278.69791666666</v>
+        <v>46283.69791666666</v>
       </c>
       <c r="B69">
-        <v>797.398</v>
+        <v>316.753</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46278.70833333334</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B70">
-        <v>814.52</v>
+        <v>335.171</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46278.71875</v>
+        <v>46283.71875</v>
       </c>
       <c r="B71">
-        <v>793.128</v>
+        <v>367.131</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46278.72916666666</v>
+        <v>46283.72916666666</v>
       </c>
       <c r="B72">
-        <v>773.705</v>
+        <v>398.191</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46278.73958333334</v>
+        <v>46283.73958333334</v>
       </c>
       <c r="B73">
-        <v>753.728</v>
+        <v>433.236</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46278.75</v>
+        <v>46283.75</v>
       </c>
       <c r="B74">
-        <v>697.6900000000001</v>
+        <v>515.484</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46278.76041666666</v>
+        <v>46283.76041666666</v>
       </c>
       <c r="B75">
-        <v>698.513</v>
+        <v>556.051</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46278.77083333334</v>
+        <v>46283.77083333334</v>
       </c>
       <c r="B76">
-        <v>700.638</v>
+        <v>596.11</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46278.78125</v>
+        <v>46283.78125</v>
       </c>
       <c r="B77">
-        <v>702.925</v>
+        <v>639.5549999999999</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46278.79166666666</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B78">
-        <v>709.741</v>
+        <v>681.9109999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46278.80208333334</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="B79">
-        <v>721.796</v>
+        <v>707.999</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46278.8125</v>
+        <v>46283.8125</v>
       </c>
       <c r="B80">
-        <v>732.838</v>
+        <v>734.85</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46278.82291666666</v>
+        <v>46283.82291666666</v>
       </c>
       <c r="B81">
-        <v>745.074</v>
+        <v>760.822</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46278.83333333334</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B82">
-        <v>773.1420000000001</v>
+        <v>784.926</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46278.84375</v>
+        <v>46283.84375</v>
       </c>
       <c r="B83">
-        <v>794.522</v>
+        <v>792.636</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46278.85416666666</v>
+        <v>46283.85416666666</v>
       </c>
       <c r="B84">
-        <v>817.8869999999999</v>
+        <v>802.188</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46278.86458333334</v>
+        <v>46283.86458333334</v>
       </c>
       <c r="B85">
-        <v>838.121</v>
+        <v>810.912</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46278.875</v>
+        <v>46283.875</v>
       </c>
       <c r="B86">
-        <v>918.673</v>
+        <v>814.213</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46278.88541666666</v>
+        <v>46283.88541666666</v>
       </c>
       <c r="B87">
-        <v>950.28</v>
+        <v>811.756</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46278.89583333334</v>
+        <v>46283.89583333334</v>
       </c>
       <c r="B88">
-        <v>981.497</v>
+        <v>807.973</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46278.90625</v>
+        <v>46283.90625</v>
       </c>
       <c r="B89">
-        <v>1014.72</v>
+        <v>803.651</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46278.91666666666</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B90">
-        <v>1053.564</v>
+        <v>790.898</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46278.92708333334</v>
+        <v>46283.92708333334</v>
       </c>
       <c r="B91">
-        <v>1086.228</v>
+        <v>773.873</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46278.9375</v>
+        <v>46283.9375</v>
       </c>
       <c r="B92">
-        <v>1121.841</v>
+        <v>756.288</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46278.94791666666</v>
+        <v>46283.94791666666</v>
       </c>
       <c r="B93">
-        <v>1155.289</v>
+        <v>738.434</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>618.601</v>
+        <v>136.157</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>599.314</v>
+        <v>129.864</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>580.867</v>
+        <v>123.973</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>562.787</v>
+        <v>118.956</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>512.5410000000001</v>
+        <v>112.728</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>497.734</v>
+        <v>110.881</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>487.199</v>
+        <v>110.116</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>469.97</v>
+        <v>108.268</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>431.401</v>
+        <v>115.442</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>409.884</v>
+        <v>114.648</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>387.977</v>
+        <v>114.395</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>373.16</v>
+        <v>113.536</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>346.589</v>
+        <v>115.019</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>332.338</v>
+        <v>115.215</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>318.156</v>
+        <v>115.141</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>303.706</v>
+        <v>115.653</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>284.167</v>
+        <v>112.199</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>271.479</v>
+        <v>111.285</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>257.365</v>
+        <v>110.193</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>246.023</v>
+        <v>109.56</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>217.855</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>206.371</v>
+        <v>107.529</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>196.169</v>
+        <v>105.641</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>185.19</v>
+        <v>103.73</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>171.223</v>
+        <v>106.586</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>169.573</v>
+        <v>103.854</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>160.092</v>
+        <v>101.672</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>158.022</v>
+        <v>88.843</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>160.344</v>
+        <v>101.673</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>154.678</v>
+        <v>91.491</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>149.956</v>
+        <v>90.738</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>146.924</v>
+        <v>90.499</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>155.155</v>
+        <v>90.29300000000001</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>149.545</v>
+        <v>90.854</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>142.418</v>
+        <v>86.83199999999999</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>136.767</v>
+        <v>84.92400000000001</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>121.629</v>
+        <v>84.988</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>126.044</v>
+        <v>84.952</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46285.39583333334</v>
       </c>
       <c r="B40">
-        <v>130.753</v>
+        <v>84.91800000000001</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46285.40625</v>
       </c>
       <c r="B41">
-        <v>135.795</v>
+        <v>83.822</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46285.41666666666</v>
       </c>
       <c r="B42">
-        <v>147.548</v>
+        <v>89.163</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46285.42708333334</v>
       </c>
       <c r="B43">
-        <v>153.511</v>
+        <v>89.744</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46285.4375</v>
       </c>
       <c r="B44">
-        <v>160.134</v>
+        <v>90.88800000000001</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46285.44791666666</v>
       </c>
       <c r="B45">
-        <v>166.188</v>
+        <v>91.866</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46285.45833333334</v>
       </c>
       <c r="B46">
-        <v>184.307</v>
+        <v>87.265</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46285.46875</v>
       </c>
       <c r="B47">
-        <v>188.589</v>
+        <v>88.42700000000001</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46285.47916666666</v>
       </c>
       <c r="B48">
-        <v>193.36</v>
+        <v>89.553</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46285.48958333334</v>
       </c>
       <c r="B49">
-        <v>196.816</v>
+        <v>90.792</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46285.5</v>
       </c>
       <c r="B50">
-        <v>206.122</v>
+        <v>92.863</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46285.51041666666</v>
       </c>
       <c r="B51">
-        <v>209.198</v>
+        <v>94.08499999999999</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46285.52083333334</v>
       </c>
       <c r="B52">
-        <v>211.707</v>
+        <v>95.732</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46285.53125</v>
       </c>
       <c r="B53">
-        <v>214.337</v>
+        <v>98.173</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46285.54166666666</v>
       </c>
       <c r="B54">
-        <v>212.487</v>
+        <v>99.09</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46285.55208333334</v>
       </c>
       <c r="B55">
-        <v>216.797</v>
+        <v>101.799</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46285.5625</v>
       </c>
       <c r="B56">
-        <v>221.003</v>
+        <v>104.625</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46285.57291666666</v>
       </c>
       <c r="B57">
-        <v>226.776</v>
+        <v>107.715</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="B58">
-        <v>232.609</v>
+        <v>113.95</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46285.59375</v>
       </c>
       <c r="B59">
-        <v>239.287</v>
+        <v>117.698</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46285.60416666666</v>
       </c>
       <c r="B60">
-        <v>246.266</v>
+        <v>121.817</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46285.61458333334</v>
       </c>
       <c r="B61">
-        <v>253.348</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46285.625</v>
       </c>
       <c r="B62">
-        <v>262.609</v>
+        <v>131.411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46285.63541666666</v>
       </c>
       <c r="B63">
-        <v>273.92</v>
+        <v>136.357</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46285.64583333334</v>
       </c>
       <c r="B64">
-        <v>284.545</v>
+        <v>143.974</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46285.65625</v>
       </c>
       <c r="B65">
-        <v>296.127</v>
+        <v>149.552</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46285.66666666666</v>
       </c>
       <c r="B66">
-        <v>270.833</v>
+        <v>152.923</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46285.67708333334</v>
       </c>
       <c r="B67">
-        <v>286.171</v>
+        <v>157.947</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46285.6875</v>
       </c>
       <c r="B68">
-        <v>301.043</v>
+        <v>163.08</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46285.69791666666</v>
       </c>
       <c r="B69">
-        <v>316.753</v>
+        <v>168.567</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46285.70833333334</v>
       </c>
       <c r="B70">
-        <v>335.171</v>
+        <v>154.486</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46285.71875</v>
       </c>
       <c r="B71">
-        <v>367.131</v>
+        <v>163.704</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46285.72916666666</v>
       </c>
       <c r="B72">
-        <v>398.191</v>
+        <v>173.41</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46285.73958333334</v>
       </c>
       <c r="B73">
-        <v>433.236</v>
+        <v>183.218</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46285.75</v>
       </c>
       <c r="B74">
-        <v>515.484</v>
+        <v>199.834</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46285.76041666666</v>
       </c>
       <c r="B75">
-        <v>556.051</v>
+        <v>216.272</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46285.77083333334</v>
       </c>
       <c r="B76">
-        <v>596.11</v>
+        <v>232.127</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46285.78125</v>
       </c>
       <c r="B77">
-        <v>639.5549999999999</v>
+        <v>248.853</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46285.79166666666</v>
       </c>
       <c r="B78">
-        <v>681.9109999999999</v>
+        <v>270.62</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46285.80208333334</v>
       </c>
       <c r="B79">
-        <v>707.999</v>
+        <v>286.998</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46285.8125</v>
       </c>
       <c r="B80">
-        <v>734.85</v>
+        <v>302.263</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46285.82291666666</v>
       </c>
       <c r="B81">
-        <v>760.822</v>
+        <v>318.743</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46285.83333333334</v>
       </c>
       <c r="B82">
-        <v>784.926</v>
+        <v>338.755</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46285.84375</v>
       </c>
       <c r="B83">
-        <v>792.636</v>
+        <v>352.943</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46285.85416666666</v>
       </c>
       <c r="B84">
-        <v>802.188</v>
+        <v>369.06</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46285.86458333334</v>
       </c>
       <c r="B85">
-        <v>810.912</v>
+        <v>384.092</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46285.875</v>
       </c>
       <c r="B86">
-        <v>814.213</v>
+        <v>397.976</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46285.88541666666</v>
       </c>
       <c r="B87">
-        <v>811.756</v>
+        <v>408.71</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46285.89583333334</v>
       </c>
       <c r="B88">
-        <v>807.973</v>
+        <v>419.024</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46285.90625</v>
       </c>
       <c r="B89">
-        <v>803.651</v>
+        <v>429.858</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46285.91666666666</v>
       </c>
       <c r="B90">
-        <v>790.898</v>
+        <v>437.478</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46285.92708333334</v>
       </c>
       <c r="B91">
-        <v>773.873</v>
+        <v>447.255</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46285.9375</v>
       </c>
       <c r="B92">
-        <v>756.288</v>
+        <v>457.858</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46285.94791666666</v>
       </c>
       <c r="B93">
-        <v>738.434</v>
+        <v>466.386</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
-        <v>136.157</v>
+        <v>2172.625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
-        <v>129.864</v>
+        <v>2181.188</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
-        <v>123.973</v>
+        <v>2185.609</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
-        <v>118.956</v>
+        <v>2184.25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
-        <v>112.728</v>
+        <v>2163.034</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
-        <v>110.881</v>
+        <v>2147.183</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
-        <v>110.116</v>
+        <v>2141.824</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
-        <v>108.268</v>
+        <v>2139.716</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
-        <v>115.442</v>
+        <v>2113.373</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
-        <v>114.648</v>
+        <v>2099.738</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
-        <v>114.395</v>
+        <v>2083.369</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
-        <v>113.536</v>
+        <v>2076.811</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
-        <v>115.019</v>
+        <v>2070.715</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
-        <v>115.215</v>
+        <v>2056.833</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
-        <v>115.141</v>
+        <v>2041.448</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
-        <v>115.653</v>
+        <v>2018.034</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
-        <v>112.199</v>
+        <v>1947.389</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
-        <v>111.285</v>
+        <v>1932.167</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
-        <v>110.193</v>
+        <v>1915.482</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
-        <v>109.56</v>
+        <v>1894.516</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
-        <v>108.32</v>
+        <v>1891.997</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
-        <v>107.529</v>
+        <v>1874.084</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
-        <v>105.641</v>
+        <v>1867.64</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
-        <v>103.73</v>
+        <v>1865.213</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
-        <v>106.586</v>
+        <v>1860.216</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>103.854</v>
+        <v>1847.021</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>101.672</v>
+        <v>1856.64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>88.843</v>
+        <v>1840.933</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>101.673</v>
+        <v>1836.052</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>91.491</v>
+        <v>1803.743</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>90.738</v>
+        <v>1757.275</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>90.499</v>
+        <v>1711.197</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>90.29300000000001</v>
+        <v>1602.262</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B35">
-        <v>90.854</v>
+        <v>1563.826</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B36">
-        <v>86.83199999999999</v>
+        <v>1539.275</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B37">
-        <v>84.92400000000001</v>
+        <v>1520.451</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B38">
-        <v>84.988</v>
+        <v>1606.825</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B39">
-        <v>84.952</v>
+        <v>1605.192</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B40">
-        <v>84.91800000000001</v>
+        <v>1617.596</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B41">
-        <v>83.822</v>
+        <v>1633.477</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B42">
-        <v>89.163</v>
+        <v>1668.897</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B43">
-        <v>89.744</v>
+        <v>1701.437</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B44">
-        <v>90.88800000000001</v>
+        <v>1735.653</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B45">
-        <v>91.866</v>
+        <v>1767.671</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B46">
-        <v>87.265</v>
+        <v>1789.801</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B47">
-        <v>88.42700000000001</v>
+        <v>1791.689</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B48">
-        <v>89.553</v>
+        <v>1792.339</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B49">
-        <v>90.792</v>
+        <v>1794.777</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B50">
-        <v>92.863</v>
+        <v>1801.897</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B51">
-        <v>94.08499999999999</v>
+        <v>1791.921</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B52">
-        <v>95.732</v>
+        <v>1779.033</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B53">
-        <v>98.173</v>
+        <v>1762.108</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B54">
-        <v>99.09</v>
+        <v>1734.363</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B55">
-        <v>101.799</v>
+        <v>1722.668</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B56">
-        <v>104.625</v>
+        <v>1711.41</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B57">
-        <v>107.715</v>
+        <v>1700.932</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B58">
-        <v>113.95</v>
+        <v>1695.419</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B59">
-        <v>117.698</v>
+        <v>1686.035</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B60">
-        <v>121.817</v>
+        <v>1675.828</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B61">
-        <v>125.69</v>
+        <v>1666.704</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B62">
-        <v>131.411</v>
+        <v>1632.653</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B63">
-        <v>136.357</v>
+        <v>1612.646</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B64">
-        <v>143.974</v>
+        <v>1592.616</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B65">
-        <v>149.552</v>
+        <v>1571.786</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B66">
-        <v>152.923</v>
+        <v>1521.933</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B67">
-        <v>157.947</v>
+        <v>1475.39</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B68">
-        <v>163.08</v>
+        <v>1425.059</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B69">
-        <v>168.567</v>
+        <v>1375.403</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B70">
-        <v>154.486</v>
+        <v>1250.616</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B71">
-        <v>163.704</v>
+        <v>1218.031</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B72">
-        <v>173.41</v>
+        <v>1187.421</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B73">
-        <v>183.218</v>
+        <v>1161.974</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B74">
-        <v>199.834</v>
+        <v>1141.301</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B75">
-        <v>216.272</v>
+        <v>1138.113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B76">
-        <v>232.127</v>
+        <v>1135.339</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B77">
-        <v>248.853</v>
+        <v>1129.314</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B78">
-        <v>270.62</v>
+        <v>1127.232</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B79">
-        <v>286.998</v>
+        <v>1135.236</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B80">
-        <v>302.263</v>
+        <v>1144.96</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B81">
-        <v>318.743</v>
+        <v>1154.996</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B82">
-        <v>338.755</v>
+        <v>1172.885</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B83">
-        <v>352.943</v>
+        <v>1182.145</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B84">
-        <v>369.06</v>
+        <v>1191.908</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B85">
-        <v>384.092</v>
+        <v>1201.264</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B86">
-        <v>397.976</v>
+        <v>1339.527</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B87">
-        <v>408.71</v>
+        <v>1367.562</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B88">
-        <v>419.024</v>
+        <v>1391.827</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B89">
-        <v>429.858</v>
+        <v>1415.457</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B90">
-        <v>437.478</v>
+        <v>1454.113</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B91">
-        <v>447.255</v>
+        <v>1491.151</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B92">
-        <v>457.858</v>
+        <v>1528.111</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B93">
-        <v>466.386</v>
+        <v>1560.86</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>2172.625</v>
+        <v>942.974</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>2181.188</v>
+        <v>965.169</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>2185.609</v>
+        <v>979.8440000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>2184.25</v>
+        <v>991.799</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>2163.034</v>
+        <v>1009.589</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>2147.183</v>
+        <v>1020.702</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>2141.824</v>
+        <v>1035.901</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>2139.716</v>
+        <v>1049.011</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>2113.373</v>
+        <v>1065.328</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>2099.738</v>
+        <v>1060.988</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>2083.369</v>
+        <v>1060.102</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>2076.811</v>
+        <v>1053.509</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>2070.715</v>
+        <v>1046.845</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>2056.833</v>
+        <v>1035.005</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>2041.448</v>
+        <v>1017.589</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>2018.034</v>
+        <v>1005.551</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>1947.389</v>
+        <v>991.264</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>1932.167</v>
+        <v>952.528</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>1915.482</v>
+        <v>928.641</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>1894.516</v>
+        <v>907.171</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>1891.997</v>
+        <v>879.26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>1874.084</v>
+        <v>853.925</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>1867.64</v>
+        <v>825.172</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>1865.213</v>
+        <v>802.749</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>1860.216</v>
+        <v>782.0359999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>1847.021</v>
+        <v>758.566</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>1856.64</v>
+        <v>728.301</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>1840.933</v>
+        <v>703.16</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>1836.052</v>
+        <v>654.216</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>1803.743</v>
+        <v>620.548</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>1757.275</v>
+        <v>585.443</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>1711.197</v>
+        <v>545.694</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>1602.262</v>
+        <v>518.378</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>1563.826</v>
+        <v>472.635</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>1539.275</v>
+        <v>443.653</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>1520.451</v>
+        <v>393.648</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>1606.825</v>
+        <v>447.66</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>1605.192</v>
+        <v>430.364</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>1617.596</v>
+        <v>417.057</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>1633.477</v>
+        <v>403.557</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>1668.897</v>
+        <v>392.084</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>1701.437</v>
+        <v>383.8</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>1735.653</v>
+        <v>374.776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>1767.671</v>
+        <v>366.253</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>1789.801</v>
+        <v>363.32</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>1791.689</v>
+        <v>348.634</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>1792.339</v>
+        <v>334.558</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>1794.777</v>
+        <v>320.301</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>1801.897</v>
+        <v>254.887</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>1791.921</v>
+        <v>243.642</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>1779.033</v>
+        <v>231.554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>1762.108</v>
+        <v>219.447</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>1734.363</v>
+        <v>205.56</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>1722.668</v>
+        <v>199.357</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>1711.41</v>
+        <v>193.083</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>1700.932</v>
+        <v>186.846</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>1695.419</v>
+        <v>181.712</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>1686.035</v>
+        <v>177.135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>1675.828</v>
+        <v>171.385</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>1666.704</v>
+        <v>166.232</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>1632.653</v>
+        <v>147.934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>1612.646</v>
+        <v>142.534</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>1592.616</v>
+        <v>136.829</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>1571.786</v>
+        <v>131.117</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>1521.933</v>
+        <v>123.305</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>1475.39</v>
+        <v>117.841</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>1425.059</v>
+        <v>112.669</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>1375.403</v>
+        <v>107.339</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>1250.616</v>
+        <v>106.343</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>1218.031</v>
+        <v>104.483</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>1187.421</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>1161.974</v>
+        <v>102.016</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>1141.301</v>
+        <v>101.053</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>1138.113</v>
+        <v>98.565</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>1135.339</v>
+        <v>96.61799999999999</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>1129.314</v>
+        <v>94.639</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>1127.232</v>
+        <v>93.69799999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>1135.236</v>
+        <v>93.331</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>1144.96</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>1154.996</v>
+        <v>92.17400000000001</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>1172.885</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>1182.145</v>
+        <v>94.212</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>1191.908</v>
+        <v>95.617</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>1201.264</v>
+        <v>97.15900000000001</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>1339.527</v>
+        <v>98.065</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>1367.562</v>
+        <v>100.403</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>1391.827</v>
+        <v>102.086</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>1415.457</v>
+        <v>104.682</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>1454.113</v>
+        <v>115.698</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>1491.151</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>1528.111</v>
+        <v>120.912</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>1560.86</v>
+        <v>123.747</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2">
-        <v>942.974</v>
+        <v>169.102</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46298.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B3">
-        <v>965.169</v>
+        <v>172.962</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46298.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B4">
-        <v>979.8440000000001</v>
+        <v>176.779</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46298.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B5">
-        <v>991.799</v>
+        <v>181.373</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46298.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B6">
-        <v>1009.589</v>
+        <v>183.045</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46298.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B7">
-        <v>1020.702</v>
+        <v>186.526</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46298.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B8">
-        <v>1035.901</v>
+        <v>189.143</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46298.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B9">
-        <v>1049.011</v>
+        <v>191.974</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46298.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B10">
-        <v>1065.328</v>
+        <v>194.656</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46298.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B11">
-        <v>1060.988</v>
+        <v>194.437</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46298.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B12">
-        <v>1060.102</v>
+        <v>194.639</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46298.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B13">
-        <v>1053.509</v>
+        <v>195.502</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46298.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B14">
-        <v>1046.845</v>
+        <v>194.722</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46298.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B15">
-        <v>1035.005</v>
+        <v>194.073</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46298.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B16">
-        <v>1017.589</v>
+        <v>193.209</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46298.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B17">
-        <v>1005.551</v>
+        <v>192.67</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46298.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B18">
-        <v>991.264</v>
+        <v>190.491</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46298.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B19">
-        <v>952.528</v>
+        <v>186.937</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46298.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B20">
-        <v>928.641</v>
+        <v>184.025</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46298.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B21">
-        <v>907.171</v>
+        <v>181.203</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46298.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B22">
-        <v>879.26</v>
+        <v>177.087</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46298.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B23">
-        <v>853.925</v>
+        <v>172.726</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46298.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B24">
-        <v>825.172</v>
+        <v>168.167</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46298.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B25">
-        <v>802.749</v>
+        <v>164.847</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B26">
-        <v>782.0359999999999</v>
+        <v>137.285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46298.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B27">
-        <v>758.566</v>
+        <v>132.868</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46298.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B28">
-        <v>728.301</v>
+        <v>129.569</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46298.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B29">
-        <v>703.16</v>
+        <v>127.252</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46298.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B30">
-        <v>654.216</v>
+        <v>134.654</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46298.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B31">
-        <v>620.548</v>
+        <v>128.085</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46298.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B32">
-        <v>585.443</v>
+        <v>113.875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46298.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B33">
-        <v>545.694</v>
+        <v>110.375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46298.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B34">
-        <v>518.378</v>
+        <v>111.843</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46298.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B35">
-        <v>472.635</v>
+        <v>109.408</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46298.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B36">
-        <v>443.653</v>
+        <v>107.066</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46298.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B37">
-        <v>393.648</v>
+        <v>104.867</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46298.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B38">
-        <v>447.66</v>
+        <v>106.428</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46298.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B39">
-        <v>430.364</v>
+        <v>105.175</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46298.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B40">
-        <v>417.057</v>
+        <v>102.986</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46298.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B41">
-        <v>403.557</v>
+        <v>101.164</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46298.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B42">
-        <v>392.084</v>
+        <v>100.088</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46298.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B43">
-        <v>383.8</v>
+        <v>99.873</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46298.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B44">
-        <v>374.776</v>
+        <v>99.908</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46298.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B45">
-        <v>366.253</v>
+        <v>99.911</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46298.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B46">
-        <v>363.32</v>
+        <v>100.242</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46298.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B47">
-        <v>348.634</v>
+        <v>100.902</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46298.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B48">
-        <v>334.558</v>
+        <v>101.518</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46298.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B49">
-        <v>320.301</v>
+        <v>101.869</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46298.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B50">
-        <v>254.887</v>
+        <v>100.307</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46298.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B51">
-        <v>243.642</v>
+        <v>100.733</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46298.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B52">
-        <v>231.554</v>
+        <v>101.39</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46298.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B53">
-        <v>219.447</v>
+        <v>101.982</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46298.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B54">
-        <v>205.56</v>
+        <v>103.727</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46298.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B55">
-        <v>199.357</v>
+        <v>105.195</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46298.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B56">
-        <v>193.083</v>
+        <v>106.561</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46298.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B57">
-        <v>186.846</v>
+        <v>107.767</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46298.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B58">
-        <v>181.712</v>
+        <v>111.741</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46298.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B59">
-        <v>177.135</v>
+        <v>111.908</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46298.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B60">
-        <v>171.385</v>
+        <v>111.951</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46298.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B61">
-        <v>166.232</v>
+        <v>112.151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46298.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B62">
-        <v>147.934</v>
+        <v>109.132</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46298.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B63">
-        <v>142.534</v>
+        <v>109.598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46298.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B64">
-        <v>136.829</v>
+        <v>109.968</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46298.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B65">
-        <v>131.117</v>
+        <v>110.053</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46298.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B66">
-        <v>123.305</v>
+        <v>121.081</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46298.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B67">
-        <v>117.841</v>
+        <v>122.384</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46298.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B68">
-        <v>112.669</v>
+        <v>123.342</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46298.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B69">
-        <v>107.339</v>
+        <v>124.935</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46298.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B70">
-        <v>106.343</v>
+        <v>121.196</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46298.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B71">
-        <v>104.483</v>
+        <v>123.975</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46298.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B72">
-        <v>103.26</v>
+        <v>126.537</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46298.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B73">
-        <v>102.016</v>
+        <v>129.661</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46298.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B74">
-        <v>101.053</v>
+        <v>134.331</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46298.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B75">
-        <v>98.565</v>
+        <v>139.548</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46298.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B76">
-        <v>96.61799999999999</v>
+        <v>143.727</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46298.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B77">
-        <v>94.639</v>
+        <v>149.084</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46298.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B78">
-        <v>93.69799999999999</v>
+        <v>155.615</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46298.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B79">
-        <v>93.331</v>
+        <v>163.938</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46298.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B80">
-        <v>92.53</v>
+        <v>173.517</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46298.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B81">
-        <v>92.17400000000001</v>
+        <v>182.073</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46298.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B82">
-        <v>93.95999999999999</v>
+        <v>189.413</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46298.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B83">
-        <v>94.212</v>
+        <v>193.733</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46298.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B84">
-        <v>95.617</v>
+        <v>199.024</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46298.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B85">
-        <v>97.15900000000001</v>
+        <v>203.507</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46298.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B86">
-        <v>98.065</v>
+        <v>204.348</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46298.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B87">
-        <v>100.403</v>
+        <v>206.27</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46298.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B88">
-        <v>102.086</v>
+        <v>208.311</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46298.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B89">
-        <v>104.682</v>
+        <v>209.937</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46298.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B90">
-        <v>115.698</v>
+        <v>212.048</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46298.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B91">
-        <v>118.11</v>
+        <v>211.211</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46298.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B92">
-        <v>120.912</v>
+        <v>210.164</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46298.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B93">
-        <v>123.747</v>
+        <v>209.406</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B477"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,738 +394,3810 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>169.102</v>
+        <v>942.974</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46299.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>172.962</v>
+        <v>965.169</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46299.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>176.779</v>
+        <v>979.8440000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46299.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>181.373</v>
+        <v>991.799</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46299.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>183.045</v>
+        <v>1009.589</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46299.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>186.526</v>
+        <v>1020.702</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46299.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>189.143</v>
+        <v>1035.901</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46299.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>191.974</v>
+        <v>1049.011</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46299.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>194.656</v>
+        <v>1065.328</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46299.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>194.437</v>
+        <v>1060.988</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46299.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>194.639</v>
+        <v>1060.102</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46299.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>195.502</v>
+        <v>1053.509</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46299.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>194.722</v>
+        <v>1046.845</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46299.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>194.073</v>
+        <v>1035.005</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46299.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>193.209</v>
+        <v>1017.589</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46299.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>192.67</v>
+        <v>1005.551</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46299.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>190.491</v>
+        <v>991.264</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46299.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>186.937</v>
+        <v>952.528</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46299.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>184.025</v>
+        <v>928.641</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46299.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>181.203</v>
+        <v>907.171</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46299.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>177.087</v>
+        <v>879.26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46299.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>172.726</v>
+        <v>853.925</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46299.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>168.167</v>
+        <v>825.172</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46299.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>164.847</v>
+        <v>802.749</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46299.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>137.285</v>
+        <v>782.0359999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46299.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>132.868</v>
+        <v>758.566</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46299.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>129.569</v>
+        <v>728.301</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46299.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>127.252</v>
+        <v>703.16</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46299.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>134.654</v>
+        <v>654.216</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46299.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>128.085</v>
+        <v>620.548</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46299.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>113.875</v>
+        <v>585.443</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46299.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>110.375</v>
+        <v>545.694</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46299.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>111.843</v>
+        <v>518.378</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46299.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>109.408</v>
+        <v>472.635</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46299.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>107.066</v>
+        <v>443.653</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46299.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>104.867</v>
+        <v>393.648</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46299.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>106.428</v>
+        <v>447.66</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46299.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>105.175</v>
+        <v>430.364</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46299.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>102.986</v>
+        <v>417.057</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46299.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>101.164</v>
+        <v>403.557</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46299.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>100.088</v>
+        <v>392.084</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46299.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>99.873</v>
+        <v>383.8</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46299.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>99.908</v>
+        <v>374.776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46299.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>99.911</v>
+        <v>366.253</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46299.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>100.242</v>
+        <v>363.32</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46299.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>100.902</v>
+        <v>348.634</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46299.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>101.518</v>
+        <v>334.558</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46299.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>101.869</v>
+        <v>320.301</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46299.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>100.307</v>
+        <v>254.887</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46299.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>100.733</v>
+        <v>243.642</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46299.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>101.39</v>
+        <v>231.554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46299.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>101.982</v>
+        <v>219.447</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46299.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>103.727</v>
+        <v>205.56</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46299.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>105.195</v>
+        <v>199.357</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46299.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>106.561</v>
+        <v>193.083</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46299.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>107.767</v>
+        <v>186.846</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46299.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>111.741</v>
+        <v>181.712</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46299.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>111.908</v>
+        <v>177.135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46299.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>111.951</v>
+        <v>171.385</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46299.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>112.151</v>
+        <v>166.232</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46299.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>109.132</v>
+        <v>147.934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46299.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>109.598</v>
+        <v>142.534</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46299.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>109.968</v>
+        <v>136.829</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46299.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>110.053</v>
+        <v>131.117</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46299.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>121.081</v>
+        <v>123.305</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46299.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>122.384</v>
+        <v>117.841</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46299.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>123.342</v>
+        <v>112.669</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46299.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>124.935</v>
+        <v>107.339</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46299.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>121.196</v>
+        <v>106.343</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46299.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>123.975</v>
+        <v>104.483</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46299.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>126.537</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46299.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>129.661</v>
+        <v>102.016</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46299.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>134.331</v>
+        <v>101.053</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46299.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>139.548</v>
+        <v>98.565</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46299.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>143.727</v>
+        <v>96.61799999999999</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46299.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>149.084</v>
+        <v>94.639</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46299.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>155.615</v>
+        <v>93.69799999999999</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46299.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>163.938</v>
+        <v>93.331</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46299.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>173.517</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46299.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>182.073</v>
+        <v>92.17400000000001</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46299.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>189.413</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46299.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>193.733</v>
+        <v>94.212</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46299.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>199.024</v>
+        <v>95.617</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46299.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>203.507</v>
+        <v>97.15900000000001</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46299.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>204.348</v>
+        <v>98.065</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46299.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>206.27</v>
+        <v>100.403</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46299.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>208.311</v>
+        <v>102.086</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46299.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>209.937</v>
+        <v>104.682</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46299.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>212.048</v>
+        <v>115.698</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46299.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>211.211</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46299.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>210.164</v>
+        <v>120.912</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
+        <v>46298.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>123.747</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>141.266</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46298.96875</v>
+      </c>
+      <c r="B95">
+        <v>146.109</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>149.565</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46298.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>153.636</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B98">
+        <v>165.702</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46299.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>169.662</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46299.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>173.479</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46299.03125</v>
+      </c>
+      <c r="B101">
+        <v>179.173</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46299.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>183.445</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46299.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>186.926</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46299.0625</v>
+      </c>
+      <c r="B104">
+        <v>187.943</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46299.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>190.974</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46299.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>190.256</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46299.09375</v>
+      </c>
+      <c r="B107">
+        <v>190.037</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46299.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>192.239</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46299.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>193.102</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46299.125</v>
+      </c>
+      <c r="B110">
+        <v>190.522</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46299.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>189.173</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46299.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>188.209</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46299.15625</v>
+      </c>
+      <c r="B113">
+        <v>187.47</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46299.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>174.791</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46299.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>171.337</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46299.1875</v>
+      </c>
+      <c r="B116">
+        <v>167.225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46299.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>164.803</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>160.887</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46299.21875</v>
+      </c>
+      <c r="B119">
+        <v>156.226</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>150.967</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46299.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>147.547</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46299.25</v>
+      </c>
+      <c r="B122">
+        <v>141.985</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46299.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>137.068</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>128.393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46299.28125</v>
+      </c>
+      <c r="B125">
+        <v>126.757</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46299.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>130.533</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46299.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>126.92</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46299.3125</v>
+      </c>
+      <c r="B128">
+        <v>115.01</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46299.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>113.785</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>113.609</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46299.34375</v>
+      </c>
+      <c r="B131">
+        <v>113.234</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>110.874</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>109.598</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>117.355</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>116.477</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>114.411</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>112.604</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>91.504</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>92.392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>90.58799999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>90.443</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>87.426</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>88.04600000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>88.678</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>89.85299999999999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>86.899</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>85.657</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>82.20999999999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>81.642</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>85.319</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>86.739</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>87.501</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>88.791</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>95.06</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>93.416</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>91.503</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>91.592</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>96.72499999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>98.89</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>99.90900000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>100.39</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>112.764</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>114.19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>115.103</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>117.017</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>127.428</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>128.807</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>131.325</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>142.181</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>126.231</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>131.548</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>136.227</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>141.384</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>134.415</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>143.738</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>156.117</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>167.673</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>179.013</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>183.433</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>188.724</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>195.107</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>201.748</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>203.87</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>201.011</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>206.437</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>211.048</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>210.311</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46299.9375</v>
+      </c>
+      <c r="B188">
+        <v>209.964</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
         <v>46299.94791666666</v>
       </c>
-      <c r="B93">
-        <v>209.406</v>
+      <c r="B189">
+        <v>208.906</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>236.746</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>230.174</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>224.488</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>226.333</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>231.103</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>233.302</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>232.181</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>227.348</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>218.595</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>217.141</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>204.303</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>197.663</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>185.683</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>181.031</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>177.01</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>173.089</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>170.631</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>171.049</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>162.601</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>144.787</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>143.652</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>139.989</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>137.783</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>125.175</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>124.344</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>123.823</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>123.281</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>117.7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>115.879</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>109.405</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>108.984</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>112.785</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>113.201</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>117.245</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>118.588</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>119.34</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>120.455</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>124.364</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>129.171</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>137.581</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>146.046</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>146.99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>141.751</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>176.884</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>171.149</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>166.376</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>157.329</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>174.164</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>175.264</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>171.545</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>172.159</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>142.325</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>149.906</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>155.037</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>159.273</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>152.436</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>158.408</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>159.527</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>166.833</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>168.949</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>160.937</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>165.015</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>167.807</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>166.518</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>179.118</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>184.702</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>181.61</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>184.582</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>181.996</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>200.913</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>155.486</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>158.757</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>141.154</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>148.051</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>135.071</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>133.979</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>135.894</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>138.049</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>173.86</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>176.87</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>178.36</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>183.685</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>175.188</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>180.229</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>178.195</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>178.939</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>177.688</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>178.552</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>174.55</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>173.696</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>178.347</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>182.239</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>182.684</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>177.329</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>179.607</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>178.421</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>179.841</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>178.28</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>180.564</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>181.776</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>182.381</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>182.078</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>192.625</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>198.456</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>201.071</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>206.948</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>209.84</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>209.157</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>215.088</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>215.398</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>202.188</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>201.628</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>196.683</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>194.838</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>197.867</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>201.402</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>208.844</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>205.826</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>184.971</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>184.957</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>180.825</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>178.989</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>158.431</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>156.239</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>146.612</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>143.428</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>157.228</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>154.134</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>155.867</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>154.734</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>154.002</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>149.122</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>146.221</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>142.532</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>154.104</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>149.289</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>148.44</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>137.635</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>170.836</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>163.989</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>158.391</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>150.774</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>142.406</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>140.578</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>147.6</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>148.029</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>150.446</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>154.996</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>157.012</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>144.659</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>120.464</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>122.817</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>128.848</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>129.938</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>128.935</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>130.333</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>131.521</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>132.261</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>123.094</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>123.185</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>122.965</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>122.686</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>121.532</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>121.137</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>128.189</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>130.212</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>104.446</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>127.326</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>104.307</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>105.128</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>115.647</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>117.576</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>120.71</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>129.503</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>133.601</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>135.19</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>139.394</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>143.464</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>149.363</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>151.302</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>153.596</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>155.861</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>149.214</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>149.304</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>150.589</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>150.99</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>152.057</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>152.065</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>152.311</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>152.379</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>161.959</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>164.158</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>163.605</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>158.337</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>169.802</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>165.04</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>162.048</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>158.004</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>144.248</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>140.163</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>136.447</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>130.44</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>124.046</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>120.452</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>116.627</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>113.147</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>108.63</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>106.823</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>104.969</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>102.639</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>96.809</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>95.057</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>94.983</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>93.13200000000001</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>89.663</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>88.899</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>88.11799999999999</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>87.56699999999999</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>90.29900000000001</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>89.754</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>86.81699999999999</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>88.173</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>87.30800000000001</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>89.407</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>91.73399999999999</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>97.084</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>119.872</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>122.889</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>125.681</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>127.61</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>131.742</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>134.296</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>136.551</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>135.848</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>146.163</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>148.556</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>154.57</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>160.283</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>172.853</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>181.93</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>191.941</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>201.514</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>221.255</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>230.994</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>239.509</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>248.563</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>266.942</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>278.504</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>289.826</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>301.06</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>315.053</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>328.251</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>350.83</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>363.877</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>388.125</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>408.743</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>429.994</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>449.058</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>480.417</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>508.274</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>538.272</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>569.506</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>601.607</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>642.779</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>686.207</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>730.755</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>779.4</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>818.375</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>854.72</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>893.5700000000001</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>928.504</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>958.126</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>985.085</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>1013.073</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>1038.149</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>1058.415</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>1079.982</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1100.115</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>1114.572</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>1127.238</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>1139.616</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46302.90625</v>
+      </c>
+      <c r="B473">
+        <v>1151.578</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>1168.146</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46302.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>1175.747</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46302.9375</v>
+      </c>
+      <c r="B476">
+        <v>1183.112</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46302.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>1188.273</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,1506 +394,1506 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>169.802</v>
+        <v>1047.446</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>165.04</v>
+        <v>1035.081</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>162.048</v>
+        <v>1024.452</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>158.004</v>
+        <v>1002.847</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>144.248</v>
+        <v>985.463</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>140.163</v>
+        <v>976.143</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>136.447</v>
+        <v>962.899</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>130.44</v>
+        <v>956.673</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>124.046</v>
+        <v>944.508</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>120.452</v>
+        <v>931.173</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>116.627</v>
+        <v>918.982</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>113.147</v>
+        <v>907.546</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>108.63</v>
+        <v>904.596</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>106.823</v>
+        <v>876.46</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>104.969</v>
+        <v>866.343</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>102.639</v>
+        <v>854.367</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>96.809</v>
+        <v>847.986</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>95.057</v>
+        <v>845.88</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>94.983</v>
+        <v>845.986</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>93.13200000000001</v>
+        <v>844.8</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>89.663</v>
+        <v>861.654</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>88.899</v>
+        <v>862.335</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>88.11799999999999</v>
+        <v>862.64</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>87.56699999999999</v>
+        <v>860.624</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>90.29900000000001</v>
+        <v>883.251</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>89.754</v>
+        <v>886.48</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>86.81699999999999</v>
+        <v>870.474</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>88.173</v>
+        <v>877.327</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>87.30800000000001</v>
+        <v>880.114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>89.407</v>
+        <v>889.495</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>91.73399999999999</v>
+        <v>898.332</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>97.084</v>
+        <v>910.925</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>119.872</v>
+        <v>922.4349999999999</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>122.889</v>
+        <v>894.984</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>125.681</v>
+        <v>872.3200000000001</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>127.61</v>
+        <v>843.4690000000001</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>131.742</v>
+        <v>844.643</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>134.296</v>
+        <v>843.095</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>136.551</v>
+        <v>848.288</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>135.848</v>
+        <v>853.222</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>146.163</v>
+        <v>883.179</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>148.556</v>
+        <v>898.984</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>154.57</v>
+        <v>916.1900000000001</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>160.283</v>
+        <v>936.092</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>172.853</v>
+        <v>964.549</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>181.93</v>
+        <v>987.485</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>191.941</v>
+        <v>1010.108</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>201.514</v>
+        <v>1031.889</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>221.255</v>
+        <v>1066.584</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>230.994</v>
+        <v>1088.592</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>239.509</v>
+        <v>1110.292</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>248.563</v>
+        <v>1129.892</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>266.942</v>
+        <v>1161.18</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>278.504</v>
+        <v>1177.675</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>289.826</v>
+        <v>1193.139</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>301.06</v>
+        <v>1208.626</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>315.053</v>
+        <v>1249.629</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>328.251</v>
+        <v>1260.393</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>350.83</v>
+        <v>1270.003</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>363.877</v>
+        <v>1277.895</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>388.125</v>
+        <v>1324.173</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>408.743</v>
+        <v>1337.145</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>429.994</v>
+        <v>1346.862</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>449.058</v>
+        <v>1360.183</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>480.417</v>
+        <v>1418.277</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>508.274</v>
+        <v>1441.013</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>538.272</v>
+        <v>1465.289</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>569.506</v>
+        <v>1492.584</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>601.607</v>
+        <v>1459.914</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>642.779</v>
+        <v>1515.691</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>686.207</v>
+        <v>1577.369</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>730.755</v>
+        <v>1629.899</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>779.4</v>
+        <v>1674.692</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>818.375</v>
+        <v>1707.773</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>854.72</v>
+        <v>1738.081</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>893.5700000000001</v>
+        <v>1766.908</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>928.504</v>
+        <v>1793.875</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>958.126</v>
+        <v>1807.205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>985.085</v>
+        <v>1820.69</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>1013.073</v>
+        <v>1835.841</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>1038.149</v>
+        <v>1854.683</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>1058.415</v>
+        <v>1858.663</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>1079.982</v>
+        <v>1857.073</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1100.115</v>
+        <v>1854.992</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1114.572</v>
+        <v>1847.867</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>1127.238</v>
+        <v>1837.619</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>1139.616</v>
+        <v>1828.412</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>1151.578</v>
+        <v>1817.62</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>1168.146</v>
+        <v>1814.557</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>1175.747</v>
+        <v>1801.449</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1183.112</v>
+        <v>1787.655</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>1188.273</v>
+        <v>1773.636</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>1118.746</v>
+        <v>1716.778</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>1117.454</v>
+        <v>1695.724</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1112.139</v>
+        <v>1693.342</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1112.222</v>
+        <v>1672.359</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>1047.446</v>
+        <v>1575.952</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>1035.081</v>
+        <v>1546.481</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1024.452</v>
+        <v>1516.98</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1002.847</v>
+        <v>1489.087</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>985.463</v>
+        <v>1452.621</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>976.143</v>
+        <v>1415.57</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>962.899</v>
+        <v>1380.673</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>956.673</v>
+        <v>1350.765</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>944.508</v>
+        <v>1312.84</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>931.173</v>
+        <v>1289.018</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>918.982</v>
+        <v>1266.494</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>907.546</v>
+        <v>1241.402</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>904.596</v>
+        <v>1205.137</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>876.46</v>
+        <v>1179.318</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>866.343</v>
+        <v>1152.648</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>854.367</v>
+        <v>1129.4</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>847.986</v>
+        <v>1073.653</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>845.88</v>
+        <v>1043.234</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>845.986</v>
+        <v>1015.382</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>844.8</v>
+        <v>987.372</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>861.654</v>
+        <v>971.984</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>862.335</v>
+        <v>943.127</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>862.64</v>
+        <v>915.84</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>860.624</v>
+        <v>887.677</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>883.251</v>
+        <v>813.304</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>886.48</v>
+        <v>786.075</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>870.474</v>
+        <v>761.053</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>877.327</v>
+        <v>743.674</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>880.114</v>
+        <v>695.553</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>889.495</v>
+        <v>671.939</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>898.332</v>
+        <v>649.144</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>910.925</v>
+        <v>629.232</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>922.4349999999999</v>
+        <v>620.977</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>894.984</v>
+        <v>595.1420000000001</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>872.3200000000001</v>
+        <v>576.188</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>843.4690000000001</v>
+        <v>546.693</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>844.643</v>
+        <v>486.069</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
-        <v>843.095</v>
+        <v>472.528</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>848.288</v>
+        <v>448.527</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>853.222</v>
+        <v>423.218</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>883.179</v>
+        <v>383.017</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
-        <v>898.984</v>
+        <v>376.493</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
-        <v>916.1900000000001</v>
+        <v>371.616</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
-        <v>936.092</v>
+        <v>369.569</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
-        <v>964.549</v>
+        <v>369.212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
-        <v>987.485</v>
+        <v>374.842</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
-        <v>1010.108</v>
+        <v>380.877</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
-        <v>1031.889</v>
+        <v>388.173</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
-        <v>1066.584</v>
+        <v>406.774</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
-        <v>1088.592</v>
+        <v>414.974</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
-        <v>1110.292</v>
+        <v>425.947</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
-        <v>1129.892</v>
+        <v>436.873</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
-        <v>1161.18</v>
+        <v>461.365</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
-        <v>1177.675</v>
+        <v>473.776</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
-        <v>1193.139</v>
+        <v>485.813</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
-        <v>1208.626</v>
+        <v>496.869</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
-        <v>1249.629</v>
+        <v>523.6660000000001</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
-        <v>1260.393</v>
+        <v>532.051</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
-        <v>1270.003</v>
+        <v>538.784</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
-        <v>1277.895</v>
+        <v>544.377</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
-        <v>1324.173</v>
+        <v>564.147</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
-        <v>1337.145</v>
+        <v>561.487</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
-        <v>1346.862</v>
+        <v>557.3339999999999</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
-        <v>1360.183</v>
+        <v>552.684</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
-        <v>1418.277</v>
+        <v>529.785</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
-        <v>1441.013</v>
+        <v>523.177</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
-        <v>1465.289</v>
+        <v>515.89</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
-        <v>1492.584</v>
+        <v>513.3869999999999</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
-        <v>1459.914</v>
+        <v>532.596</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
-        <v>1515.691</v>
+        <v>538.23</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
-        <v>1577.369</v>
+        <v>539.0359999999999</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
-        <v>1629.899</v>
+        <v>543.472</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
-        <v>1674.692</v>
+        <v>583.511</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
-        <v>1707.773</v>
+        <v>588.927</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
-        <v>1738.081</v>
+        <v>595.446</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
-        <v>1766.908</v>
+        <v>604.955</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
-        <v>1793.875</v>
+        <v>627.329</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
-        <v>1807.205</v>
+        <v>638.783</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
-        <v>1820.69</v>
+        <v>646.452</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
-        <v>1835.841</v>
+        <v>648.711</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
-        <v>1854.683</v>
+        <v>623.946</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
-        <v>1858.663</v>
+        <v>626.621</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
-        <v>1857.073</v>
+        <v>630.362</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
-        <v>1854.992</v>
+        <v>636.141</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
-        <v>1847.867</v>
+        <v>639.078</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
-        <v>1837.619</v>
+        <v>651.275</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B184">
-        <v>1828.412</v>
+        <v>671.658</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B185">
-        <v>1817.62</v>
+        <v>697.634</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B186">
-        <v>1814.557</v>
+        <v>741.503</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B187">
-        <v>1801.449</v>
+        <v>765.87</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B188">
-        <v>1787.655</v>
+        <v>792.913</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B189">
-        <v>1773.636</v>
+        <v>815.336</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>935.28</v>
+        <v>1941.64</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>897.212</v>
+        <v>1957.481</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>860.513</v>
+        <v>1973.214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>808.576</v>
+        <v>1988.772</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>723.9589999999999</v>
+        <v>1980.982</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>694.572</v>
+        <v>2017.875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>665.443</v>
+        <v>2041.072</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>628.763</v>
+        <v>2052.74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>608.696</v>
+        <v>2060.445</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>596.585</v>
+        <v>2057.801</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>582.4829999999999</v>
+        <v>2058.189</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>574.008</v>
+        <v>2056.84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>586.0309999999999</v>
+        <v>2037.552</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>583.832</v>
+        <v>2042.185</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>589.158</v>
+        <v>2048.055</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>595.721</v>
+        <v>2051.478</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>620.583</v>
+        <v>2055.868</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>636.164</v>
+        <v>2054.967</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>657.821</v>
+        <v>2051.248</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>678.283</v>
+        <v>2053.857</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>746.412</v>
+        <v>2104.469</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>778.248</v>
+        <v>2111.796</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>787.473</v>
+        <v>2118.405</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>817.22</v>
+        <v>2124.492</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>789.324</v>
+        <v>2113.498</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>809.117</v>
+        <v>2128.737</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>817.35</v>
+        <v>2132.841</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>831.064</v>
+        <v>2145.936</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>915.611</v>
+        <v>2182.844</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>913.2140000000001</v>
+        <v>2224.695</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>914.5</v>
+        <v>2261.349</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>917.663</v>
+        <v>2266.463</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>802.996</v>
+        <v>2271.582</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>809.417</v>
+        <v>2274.897</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>816.022</v>
+        <v>2260.406</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>822.0890000000001</v>
+        <v>2262.916</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>795.671</v>
+        <v>2238.129</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>800.687</v>
+        <v>2249.516</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>807.314</v>
+        <v>2257.31</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>813.246</v>
+        <v>2265.23</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>850.569</v>
+        <v>2247.099</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>857.36</v>
+        <v>2267.11</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>864.919</v>
+        <v>2286.18</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>872.048</v>
+        <v>2305.898</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>894.274</v>
+        <v>2329.751</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>899.135</v>
+        <v>2339.796</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>904.255</v>
+        <v>2351.296</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>908.457</v>
+        <v>2361.946</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>922.9299999999999</v>
+        <v>2333.141</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>928.495</v>
+        <v>2339.899</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>931.785</v>
+        <v>2346.417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>935.991</v>
+        <v>2353.978</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>957.833</v>
+        <v>2347.053</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>967.715</v>
+        <v>2353.852</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>979.6180000000001</v>
+        <v>2357.706</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>988.706</v>
+        <v>2361.414</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>1026.044</v>
+        <v>2380.025</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>1044.331</v>
+        <v>2382.058</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>1063.788</v>
+        <v>2379.138</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>1084.793</v>
+        <v>2381.592</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>1125.224</v>
+        <v>2346.183</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>1148.403</v>
+        <v>2342.452</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>1171.189</v>
+        <v>2333.291</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>1194.605</v>
+        <v>2324.024</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>1234.616</v>
+        <v>2304.594</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>1264.756</v>
+        <v>2296.569</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>1294.29</v>
+        <v>2288.237</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>1324.912</v>
+        <v>2280.087</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>1361.38</v>
+        <v>2265.647</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>1396.876</v>
+        <v>2272.405</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>1431.895</v>
+        <v>2280.394</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>1468.284</v>
+        <v>2289.333</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>1515.371</v>
+        <v>2293.876</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>1546.394</v>
+        <v>2295.821</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>1578.46</v>
+        <v>2303.508</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>1609.067</v>
+        <v>2304.376</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>1641.225</v>
+        <v>2306.063</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>1669.41</v>
+        <v>2304.435</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>1698.167</v>
+        <v>2303.44</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>1724.591</v>
+        <v>2302.711</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>1754.13</v>
+        <v>2305.963</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>1770.683</v>
+        <v>2300.354</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>1787.49</v>
+        <v>2296.98</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>1799.805</v>
+        <v>2292.754</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>1809.15</v>
+        <v>2317.27</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>1819.12</v>
+        <v>2316.237</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>1829.227</v>
+        <v>2313.366</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>1841.686</v>
+        <v>2314.597</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>1849.762</v>
+        <v>2329.79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>1862.323</v>
+        <v>2332.851</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>1872.522</v>
+        <v>2335.233</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>1884.267</v>
+        <v>2337.297</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
-        <v>1941.64</v>
+        <v>2454.623</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
-        <v>1957.481</v>
+        <v>2454.535</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
-        <v>1973.214</v>
+        <v>2452.395</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
-        <v>1988.772</v>
+        <v>2453.732</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
-        <v>1980.982</v>
+        <v>2444.137</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
-        <v>2017.875</v>
+        <v>2443.466</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
-        <v>2041.072</v>
+        <v>2441.667</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
-        <v>2052.74</v>
+        <v>2438.431</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
-        <v>2060.445</v>
+        <v>2440.881</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
-        <v>2057.801</v>
+        <v>2433.954</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
-        <v>2058.189</v>
+        <v>2429.397</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
-        <v>2056.84</v>
+        <v>2420.925</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
-        <v>2037.552</v>
+        <v>2419.846</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
-        <v>2042.185</v>
+        <v>2417.313</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
-        <v>2048.055</v>
+        <v>2420.971</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
-        <v>2051.478</v>
+        <v>2409.355</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
-        <v>2055.868</v>
+        <v>2381.823</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
-        <v>2054.967</v>
+        <v>2384.713</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
-        <v>2051.248</v>
+        <v>2385.622</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
-        <v>2053.857</v>
+        <v>2388.234</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
-        <v>2104.469</v>
+        <v>2479.054</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
-        <v>2111.796</v>
+        <v>2482.633</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
-        <v>2118.405</v>
+        <v>2485.628</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
-        <v>2124.492</v>
+        <v>2491.009</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
-        <v>2113.498</v>
+        <v>2432.847</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
-        <v>2128.737</v>
+        <v>2423.243</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
-        <v>2132.841</v>
+        <v>2410.11</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>2145.936</v>
+        <v>2402.078</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>2182.844</v>
+        <v>2375.157</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>2224.695</v>
+        <v>2376.279</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
-        <v>2261.349</v>
+        <v>2366.567</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
-        <v>2266.463</v>
+        <v>2351.05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
-        <v>2271.582</v>
+        <v>2287.961</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
-        <v>2274.897</v>
+        <v>2297.147</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
-        <v>2260.406</v>
+        <v>2302.8</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>2262.916</v>
+        <v>2312.624</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>2238.129</v>
+        <v>2330.181</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>2249.516</v>
+        <v>2334.173</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>2257.31</v>
+        <v>2340.315</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>2265.23</v>
+        <v>2347.987</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>2247.099</v>
+        <v>2355.544</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>2267.11</v>
+        <v>2350.134</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>2286.18</v>
+        <v>2344.889</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>2305.898</v>
+        <v>2339.392</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>2329.751</v>
+        <v>2301.593</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
-        <v>2339.796</v>
+        <v>2303.708</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
-        <v>2351.296</v>
+        <v>2304.703</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
-        <v>2361.946</v>
+        <v>2305.973</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>2333.141</v>
+        <v>2308.768</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>2339.899</v>
+        <v>2304.492</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>2346.417</v>
+        <v>2297.336</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>2353.978</v>
+        <v>2288.318</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>2347.053</v>
+        <v>2317.614</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>2353.852</v>
+        <v>2300.315</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>2357.706</v>
+        <v>2280.91</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B57">
-        <v>2361.414</v>
+        <v>2263.522</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B58">
-        <v>2380.025</v>
+        <v>2230.336</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B59">
-        <v>2382.058</v>
+        <v>2205.166</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B60">
-        <v>2379.138</v>
+        <v>2178.262</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B61">
-        <v>2381.592</v>
+        <v>2154.155</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B62">
-        <v>2346.183</v>
+        <v>2138.321</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B63">
-        <v>2342.452</v>
+        <v>2110.205</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B64">
-        <v>2333.291</v>
+        <v>2080.831</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B65">
-        <v>2324.024</v>
+        <v>2050.827</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B66">
-        <v>2304.594</v>
+        <v>2018.127</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B67">
-        <v>2296.569</v>
+        <v>1967.294</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B68">
-        <v>2288.237</v>
+        <v>1919.104</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B69">
-        <v>2280.087</v>
+        <v>1873.846</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B70">
-        <v>2265.647</v>
+        <v>1807.618</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B71">
-        <v>2272.405</v>
+        <v>1762.15</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B72">
-        <v>2280.394</v>
+        <v>1716.06</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B73">
-        <v>2289.333</v>
+        <v>1674.125</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B74">
-        <v>2293.876</v>
+        <v>1676.529</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B75">
-        <v>2295.821</v>
+        <v>1657.854</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B76">
-        <v>2303.508</v>
+        <v>1636.225</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B77">
-        <v>2304.376</v>
+        <v>1616.017</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B78">
-        <v>2306.063</v>
+        <v>1598.004</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B79">
-        <v>2304.435</v>
+        <v>1596.037</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B80">
-        <v>2303.44</v>
+        <v>1593.61</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B81">
-        <v>2302.711</v>
+        <v>1591.66</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B82">
-        <v>2305.963</v>
+        <v>1589.105</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B83">
-        <v>2300.354</v>
+        <v>1582.822</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B84">
-        <v>2296.98</v>
+        <v>1574.842</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B85">
-        <v>2292.754</v>
+        <v>1566.252</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B86">
-        <v>2317.27</v>
+        <v>1559.561</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B87">
-        <v>2316.237</v>
+        <v>1557.678</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B88">
-        <v>2313.366</v>
+        <v>1554.838</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B89">
-        <v>2314.597</v>
+        <v>1552.265</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B90">
-        <v>2329.79</v>
+        <v>1547.213</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46309.92708333334</v>
       </c>
       <c r="B91">
-        <v>2332.851</v>
+        <v>1543.284</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46309.9375</v>
       </c>
       <c r="B92">
-        <v>2335.233</v>
+        <v>1547.448</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46309.94791666666</v>
       </c>
       <c r="B93">
-        <v>2337.297</v>
+        <v>1552.923</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>2454.623</v>
+        <v>1580.982</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>2454.535</v>
+        <v>1575.836</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>2452.395</v>
+        <v>1582.94</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>2453.732</v>
+        <v>1571.718</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>2444.137</v>
+        <v>1534.452</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>2443.466</v>
+        <v>1522.574</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>2441.667</v>
+        <v>1515.981</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>2438.431</v>
+        <v>1505.17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>2440.881</v>
+        <v>1469.421</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>2433.954</v>
+        <v>1461.798</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>2429.397</v>
+        <v>1448.094</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
-        <v>2420.925</v>
+        <v>1460.27</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>2419.846</v>
+        <v>1444.246</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>2417.313</v>
+        <v>1431.126</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>2420.971</v>
+        <v>1424.831</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>2409.355</v>
+        <v>1422.514</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>2381.823</v>
+        <v>1424.231</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>2384.713</v>
+        <v>1404.097</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>2385.622</v>
+        <v>1394.278</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>2388.234</v>
+        <v>1374.658</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>2479.054</v>
+        <v>1366.209</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>2482.633</v>
+        <v>1357.363</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>2485.628</v>
+        <v>1350.17</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>2491.009</v>
+        <v>1342.49</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>2432.847</v>
+        <v>1279.213</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>2423.243</v>
+        <v>1265.283</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>2410.11</v>
+        <v>1251.974</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>2402.078</v>
+        <v>1245.114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>2375.157</v>
+        <v>1227.887</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>2376.279</v>
+        <v>1213.85</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>2366.567</v>
+        <v>1192.769</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>2351.05</v>
+        <v>1177.878</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>2287.961</v>
+        <v>1256.566</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>2297.147</v>
+        <v>1267.498</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>2302.8</v>
+        <v>1290.019</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>2312.624</v>
+        <v>1283.328</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>2330.181</v>
+        <v>1267.766</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>2334.173</v>
+        <v>1280.532</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>2340.315</v>
+        <v>1293.744</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>2347.987</v>
+        <v>1308.65</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>2355.544</v>
+        <v>1280.942</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>2350.134</v>
+        <v>1293.842</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>2344.889</v>
+        <v>1308.062</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>2339.392</v>
+        <v>1318.602</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>2301.593</v>
+        <v>1358.6</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>2303.708</v>
+        <v>1366.415</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>2304.703</v>
+        <v>1372.395</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>2305.973</v>
+        <v>1376.25</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>2308.768</v>
+        <v>1364.006</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>2304.492</v>
+        <v>1358.348</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>2297.336</v>
+        <v>1352.003</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B53">
-        <v>2288.318</v>
+        <v>1343.992</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B54">
-        <v>2317.614</v>
+        <v>1336.513</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B55">
-        <v>2300.315</v>
+        <v>1331.115</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B56">
-        <v>2280.91</v>
+        <v>1326.533</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B57">
-        <v>2263.522</v>
+        <v>1320.661</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B58">
-        <v>2230.336</v>
+        <v>1331.763</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B59">
-        <v>2205.166</v>
+        <v>1322.832</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B60">
-        <v>2178.262</v>
+        <v>1308.915</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B61">
-        <v>2154.155</v>
+        <v>1297.927</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B62">
-        <v>2138.321</v>
+        <v>1267.886</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B63">
-        <v>2110.205</v>
+        <v>1250.787</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B64">
-        <v>2080.831</v>
+        <v>1231.544</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B65">
-        <v>2050.827</v>
+        <v>1211.62</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B66">
-        <v>2018.127</v>
+        <v>1057.421</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B67">
-        <v>1967.294</v>
+        <v>1027.365</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B68">
-        <v>1919.104</v>
+        <v>998.605</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B69">
-        <v>1873.846</v>
+        <v>968.1130000000001</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B70">
-        <v>1807.618</v>
+        <v>974.2430000000001</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B71">
-        <v>1762.15</v>
+        <v>966.776</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B72">
-        <v>1716.06</v>
+        <v>959.078</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B73">
-        <v>1674.125</v>
+        <v>953.099</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B74">
-        <v>1676.529</v>
+        <v>946.223</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B75">
-        <v>1657.854</v>
+        <v>939.279</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B76">
-        <v>1636.225</v>
+        <v>934.9160000000001</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B77">
-        <v>1616.017</v>
+        <v>930.221</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B78">
-        <v>1598.004</v>
+        <v>933.617</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B79">
-        <v>1596.037</v>
+        <v>931.436</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B80">
-        <v>1593.61</v>
+        <v>931.423</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B81">
-        <v>1591.66</v>
+        <v>929.6369999999999</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B82">
-        <v>1589.105</v>
+        <v>945.0549999999999</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B83">
-        <v>1582.822</v>
+        <v>943.747</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B84">
-        <v>1574.842</v>
+        <v>943.3339999999999</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B85">
-        <v>1566.252</v>
+        <v>941.231</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B86">
-        <v>1559.561</v>
+        <v>931.573</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B87">
-        <v>1557.678</v>
+        <v>933.4829999999999</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B88">
-        <v>1554.838</v>
+        <v>933.758</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B89">
-        <v>1552.265</v>
+        <v>934.4349999999999</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B90">
-        <v>1547.213</v>
+        <v>940.535</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46309.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B91">
-        <v>1543.284</v>
+        <v>944.9640000000001</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46309.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B92">
-        <v>1547.448</v>
+        <v>953.845</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46309.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B93">
-        <v>1552.923</v>
+        <v>965.016</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>1580.982</v>
+        <v>575.335</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>1575.836</v>
+        <v>566.782</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>1582.94</v>
+        <v>558.311</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>1571.718</v>
+        <v>549.244</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>1534.452</v>
+        <v>553.963</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>1522.574</v>
+        <v>555.462</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
-        <v>1515.981</v>
+        <v>549.395</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>1505.17</v>
+        <v>539.942</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>1469.421</v>
+        <v>515.899</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
-        <v>1461.798</v>
+        <v>516.421</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>1448.094</v>
+        <v>521.8099999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
-        <v>1460.27</v>
+        <v>521.904</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>1444.246</v>
+        <v>541.598</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>1431.126</v>
+        <v>545.636</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>1424.831</v>
+        <v>550.8869999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>1422.514</v>
+        <v>559.639</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>1424.231</v>
+        <v>578.811</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>1404.097</v>
+        <v>585.715</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
-        <v>1394.278</v>
+        <v>593.921</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
-        <v>1374.658</v>
+        <v>603.081</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
-        <v>1366.209</v>
+        <v>605.341</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
-        <v>1357.363</v>
+        <v>611.621</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>1350.17</v>
+        <v>614.4349999999999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>1342.49</v>
+        <v>623.889</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>1279.213</v>
+        <v>611.425</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>1265.283</v>
+        <v>618.261</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>1251.974</v>
+        <v>630.205</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>1245.114</v>
+        <v>631.958</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>1227.887</v>
+        <v>609.3630000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>1213.85</v>
+        <v>612.254</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>1192.769</v>
+        <v>625.27</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>1177.878</v>
+        <v>626.982</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>1256.566</v>
+        <v>699.966</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>1267.498</v>
+        <v>700.119</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>1290.019</v>
+        <v>701.492</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B37">
-        <v>1283.328</v>
+        <v>697.279</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B38">
-        <v>1267.766</v>
+        <v>667.239</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B39">
-        <v>1280.532</v>
+        <v>684.149</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B40">
-        <v>1293.744</v>
+        <v>698.453</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B41">
-        <v>1308.65</v>
+        <v>713.4450000000001</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B42">
-        <v>1280.942</v>
+        <v>705.95</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B43">
-        <v>1293.842</v>
+        <v>721.025</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B44">
-        <v>1308.062</v>
+        <v>736.481</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B45">
-        <v>1318.602</v>
+        <v>748.211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B46">
-        <v>1358.6</v>
+        <v>800.8</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B47">
-        <v>1366.415</v>
+        <v>814.471</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B48">
-        <v>1372.395</v>
+        <v>841.831</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B49">
-        <v>1376.25</v>
+        <v>854.605</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B50">
-        <v>1364.006</v>
+        <v>881.051</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B51">
-        <v>1358.348</v>
+        <v>895.157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B52">
-        <v>1352.003</v>
+        <v>909.141</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B53">
-        <v>1343.992</v>
+        <v>923.009</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B54">
-        <v>1336.513</v>
+        <v>942.269</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B55">
-        <v>1331.115</v>
+        <v>957.739</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B56">
-        <v>1326.533</v>
+        <v>973.726</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B57">
-        <v>1320.661</v>
+        <v>990.8869999999999</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B58">
-        <v>1331.763</v>
+        <v>1044.467</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B59">
-        <v>1322.832</v>
+        <v>1072.247</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B60">
-        <v>1308.915</v>
+        <v>1098.085</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B61">
-        <v>1297.927</v>
+        <v>1123.953</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B62">
-        <v>1267.886</v>
+        <v>1108.464</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B63">
-        <v>1250.787</v>
+        <v>1137.986</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B64">
-        <v>1231.544</v>
+        <v>1168.455</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B65">
-        <v>1211.62</v>
+        <v>1194.973</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B66">
-        <v>1057.421</v>
+        <v>1212.557</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B67">
-        <v>1027.365</v>
+        <v>1252.87</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B68">
-        <v>998.605</v>
+        <v>1289.963</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B69">
-        <v>968.1130000000001</v>
+        <v>1320.553</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B70">
-        <v>974.2430000000001</v>
+        <v>1369.452</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B71">
-        <v>966.776</v>
+        <v>1404.117</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B72">
-        <v>959.078</v>
+        <v>1443.435</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B73">
-        <v>953.099</v>
+        <v>1480.117</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B74">
-        <v>946.223</v>
+        <v>1574.901</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B75">
-        <v>939.279</v>
+        <v>1590.373</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B76">
-        <v>934.9160000000001</v>
+        <v>1606.308</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B77">
-        <v>930.221</v>
+        <v>1621.973</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B78">
-        <v>933.617</v>
+        <v>1667.364</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B79">
-        <v>931.436</v>
+        <v>1677.171</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B80">
-        <v>931.423</v>
+        <v>1683.382</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B81">
-        <v>929.6369999999999</v>
+        <v>1688.427</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B82">
-        <v>945.0549999999999</v>
+        <v>1688.314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B83">
-        <v>943.747</v>
+        <v>1692.062</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B84">
-        <v>943.3339999999999</v>
+        <v>1691.531</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B85">
-        <v>941.231</v>
+        <v>1689.731</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B86">
-        <v>931.573</v>
+        <v>1688.268</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B87">
-        <v>933.4829999999999</v>
+        <v>1689.631</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B88">
-        <v>933.758</v>
+        <v>1692.048</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B89">
-        <v>934.4349999999999</v>
+        <v>1692.881</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B90">
-        <v>940.535</v>
+        <v>1666.074</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B91">
-        <v>944.9640000000001</v>
+        <v>1664.411</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B92">
-        <v>953.845</v>
+        <v>1667.802</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B93">
-        <v>965.016</v>
+        <v>1674.037</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,738 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
-        <v>575.335</v>
+        <v>169.093</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
-        <v>566.782</v>
+        <v>149.652</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
-        <v>558.311</v>
+        <v>145.865</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
-        <v>549.244</v>
+        <v>141.217</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
-        <v>553.963</v>
+        <v>136.787</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
-        <v>555.462</v>
+        <v>132.449</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
-        <v>549.395</v>
+        <v>127.688</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
-        <v>539.942</v>
+        <v>123.345</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
-        <v>515.899</v>
+        <v>119.398</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
-        <v>516.421</v>
+        <v>115.603</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
-        <v>521.8099999999999</v>
+        <v>111.982</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
-        <v>521.904</v>
+        <v>108.435</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
-        <v>541.598</v>
+        <v>105.717</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
-        <v>545.636</v>
+        <v>103.527</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
-        <v>550.8869999999999</v>
+        <v>101.014</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
-        <v>559.639</v>
+        <v>98.586</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
-        <v>578.811</v>
+        <v>96.89400000000001</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
-        <v>585.715</v>
+        <v>94.911</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
-        <v>593.921</v>
+        <v>93.05500000000001</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
-        <v>603.081</v>
+        <v>91.589</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
-        <v>605.341</v>
+        <v>92.322</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
-        <v>611.621</v>
+        <v>91.13200000000001</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
-        <v>614.4349999999999</v>
+        <v>90.001</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
-        <v>623.889</v>
+        <v>103.114</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
-        <v>611.425</v>
+        <v>103.703</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
-        <v>618.261</v>
+        <v>85.43300000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
-        <v>630.205</v>
+        <v>84.491</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
-        <v>631.958</v>
+        <v>84.071</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>609.3630000000001</v>
+        <v>88.056</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>612.254</v>
+        <v>88.148</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>625.27</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>626.982</v>
+        <v>92.47</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>699.966</v>
+        <v>94.08199999999999</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>700.119</v>
+        <v>94.273</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>701.492</v>
+        <v>94.673</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B37">
-        <v>697.279</v>
+        <v>94.95699999999999</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B38">
-        <v>667.239</v>
+        <v>96.02500000000001</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B39">
-        <v>684.149</v>
+        <v>97.774</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B40">
-        <v>698.453</v>
+        <v>98.64</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B41">
-        <v>713.4450000000001</v>
+        <v>99.28100000000001</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B42">
-        <v>705.95</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B43">
-        <v>721.025</v>
+        <v>108.173</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B44">
-        <v>736.481</v>
+        <v>111.458</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B45">
-        <v>748.211</v>
+        <v>115.179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B46">
-        <v>800.8</v>
+        <v>119.995</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B47">
-        <v>814.471</v>
+        <v>124.17</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B48">
-        <v>841.831</v>
+        <v>127.471</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B49">
-        <v>854.605</v>
+        <v>130.574</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B50">
-        <v>881.051</v>
+        <v>133.123</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B51">
-        <v>895.157</v>
+        <v>135.721</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B52">
-        <v>909.141</v>
+        <v>137.915</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B53">
-        <v>923.009</v>
+        <v>140.452</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B54">
-        <v>942.269</v>
+        <v>143.141</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B55">
-        <v>957.739</v>
+        <v>146.106</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B56">
-        <v>973.726</v>
+        <v>148.758</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B57">
-        <v>990.8869999999999</v>
+        <v>151.472</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B58">
-        <v>1044.467</v>
+        <v>152.468</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B59">
-        <v>1072.247</v>
+        <v>154.53</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B60">
-        <v>1098.085</v>
+        <v>156.772</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B61">
-        <v>1123.953</v>
+        <v>159.02</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B62">
-        <v>1108.464</v>
+        <v>163.131</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B63">
-        <v>1137.986</v>
+        <v>165.161</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B64">
-        <v>1168.455</v>
+        <v>167.569</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B65">
-        <v>1194.973</v>
+        <v>173.015</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B66">
-        <v>1212.557</v>
+        <v>180.234</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B67">
-        <v>1252.87</v>
+        <v>190.504</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B68">
-        <v>1289.963</v>
+        <v>200.692</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B69">
-        <v>1320.553</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B70">
-        <v>1369.452</v>
+        <v>225.598</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B71">
-        <v>1404.117</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B72">
-        <v>1443.435</v>
+        <v>254.72</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B73">
-        <v>1480.117</v>
+        <v>269.035</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B74">
-        <v>1574.901</v>
+        <v>288.274</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B75">
-        <v>1590.373</v>
+        <v>302.36</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B76">
-        <v>1606.308</v>
+        <v>316.69</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B77">
-        <v>1621.973</v>
+        <v>331.476</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B78">
-        <v>1667.364</v>
+        <v>346.991</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B79">
-        <v>1677.171</v>
+        <v>359.803</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B80">
-        <v>1683.382</v>
+        <v>372.271</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B81">
-        <v>1688.427</v>
+        <v>384.821</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B82">
-        <v>1688.314</v>
+        <v>398.206</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B83">
-        <v>1692.062</v>
+        <v>408.986</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B84">
-        <v>1691.531</v>
+        <v>420.397</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B85">
-        <v>1689.731</v>
+        <v>430.428</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B86">
-        <v>1688.268</v>
+        <v>439.448</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B87">
-        <v>1689.631</v>
+        <v>442.483</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B88">
-        <v>1692.048</v>
+        <v>444.649</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B89">
-        <v>1692.881</v>
+        <v>447.371</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B90">
-        <v>1666.074</v>
+        <v>445.992</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B91">
-        <v>1664.411</v>
+        <v>444.703</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B92">
-        <v>1667.802</v>
+        <v>440.457</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B93">
-        <v>1674.037</v>
+        <v>439.466</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46320.91666666666</v>
+      </c>
+      <c r="B94">
+        <v>431.57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46320.92708333334</v>
+      </c>
+      <c r="B95">
+        <v>424.995</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46320.9375</v>
+      </c>
+      <c r="B96">
+        <v>421.639</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46320.94791666666</v>
+      </c>
+      <c r="B97">
+        <v>420.161</v>
       </c>
     </row>
   </sheetData>
